--- a/Employee_Reports_wi48/Edison Mendoza Rojas Q0505.xlsx
+++ b/Employee_Reports_wi48/Edison Mendoza Rojas Q0505.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1549,11 +1549,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1598,11 +1598,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1647,11 +1647,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1696,11 +1696,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1745,11 +1745,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1794,11 +1794,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1831,11 +1831,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1880,11 +1880,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1929,11 +1929,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1979,11 +1979,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2065,11 +2065,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2114,11 +2114,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-113</v>
+        <v>-116</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2163,11 +2163,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2212,11 +2212,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-114</v>
+        <v>-117</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2235,9 +2235,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>10-May-2025</t>
@@ -2249,11 +2261,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-64</v>
+        <v>-67</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2298,11 +2310,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2321,9 +2333,21 @@
           <t>Equipment Operation Procedure(QDF-SOP-003) (SOPs)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>DFWH</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>LSME-QDF-SOP-003</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>07-May-2025</t>
@@ -2335,11 +2359,11 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-67</v>
+        <v>-70</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2384,11 +2408,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2421,11 +2445,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2470,11 +2494,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2507,11 +2531,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2544,11 +2568,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2593,11 +2617,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2642,11 +2666,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2691,11 +2715,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -2728,11 +2752,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -2765,11 +2789,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -2802,11 +2826,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -2839,11 +2863,11 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -3521,7 +3545,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7650</v>
+        <v>7647</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3550,7 +3574,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3645,7 +3669,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7981</v>
+        <v>7978</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3674,7 +3698,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7977</v>
+        <v>7974</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3703,7 +3727,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7976</v>
+        <v>7973</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3732,7 +3756,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7983</v>
+        <v>7980</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
